--- a/wwwroot/assets/js/map/map_data/ecosystem_and_biodiversity/bioecological_zone/bioecological_zone/legendcolor_bioecologicalzone.xlsx
+++ b/wwwroot/assets/js/map/map_data/ecosystem_and_biodiversity/bioecological_zone/bioecological_zone/legendcolor_bioecologicalzone.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\CRS\For RMO\bioecological_zone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\CRS\Complete File\FInal Files\BEZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698A82FE-A5F9-43AB-90FD-5A4D1535A5C8}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4B13C9-5B79-470D-A412-8988D1840D7B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,88 +18,13 @@
   <definedNames>
     <definedName name="_xlnm.Database">BEZ!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="179021"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
-    <t>Barind Tract</t>
-  </si>
-  <si>
-    <t>Brahmaputra-Jamuna Floodplain</t>
-  </si>
-  <si>
-    <t>Chakaria Sundarban</t>
-  </si>
-  <si>
-    <t>Chalan Beel</t>
-  </si>
-  <si>
-    <t>Chittagong Hills and The CHTs</t>
-  </si>
-  <si>
-    <t>Coastal Marine Water</t>
-  </si>
-  <si>
-    <t>Coastal Plains</t>
-  </si>
-  <si>
-    <t>Ganges Floodplain</t>
-  </si>
-  <si>
-    <t>Gopalgonj/ Khulna Peat Lands</t>
-  </si>
-  <si>
-    <t>Haor Basin</t>
-  </si>
-  <si>
-    <t>Himalayan Piedmont Plain</t>
-  </si>
-  <si>
-    <t>Kaptai Lake</t>
-  </si>
-  <si>
-    <t>Lalmai Tiperah Hills</t>
-  </si>
-  <si>
-    <t>Madhupur Sal Tract</t>
-  </si>
-  <si>
-    <t>Major Rivers</t>
-  </si>
-  <si>
-    <t>Meghna Eastuarine Floodplain</t>
-  </si>
-  <si>
-    <t>Meghna Floodplain</t>
-  </si>
-  <si>
-    <t>Narikel Jinjira Coaral Island</t>
-  </si>
-  <si>
-    <t>Offshore Islands</t>
-  </si>
-  <si>
-    <t>Saline Tidal Floodplain</t>
-  </si>
-  <si>
-    <t>Sandy Beach/Sand Dunes</t>
-  </si>
-  <si>
-    <t>Sundarbans</t>
-  </si>
-  <si>
-    <t>Surma-Kushiara Floodplain</t>
-  </si>
-  <si>
-    <t>Sylhet Hills</t>
-  </si>
-  <si>
-    <t>Teesta Floodplain</t>
-  </si>
-  <si>
     <t>layer_main_attribure_value</t>
   </si>
   <si>
@@ -185,6 +110,81 @@
   </si>
   <si>
     <t>layer_legend_display_name (Name of zones)</t>
+  </si>
+  <si>
+    <t>2. Barind Tract</t>
+  </si>
+  <si>
+    <t>1. Himalayan Piedmont Plain</t>
+  </si>
+  <si>
+    <t>3. Madhupur Sal Tract</t>
+  </si>
+  <si>
+    <t>4a.Teesta Floodplain</t>
+  </si>
+  <si>
+    <t>4b.Ganges Floodplain</t>
+  </si>
+  <si>
+    <t>4c.Brahmaputra-Jamuna Floodplain</t>
+  </si>
+  <si>
+    <t>4d.Surma-Kushiara Floodplain</t>
+  </si>
+  <si>
+    <t>4e.Meghna Floodplain</t>
+  </si>
+  <si>
+    <t>5a.Haor Basin</t>
+  </si>
+  <si>
+    <t>5b.Chalan Beel</t>
+  </si>
+  <si>
+    <t>5c.Kaptai Lake</t>
+  </si>
+  <si>
+    <t>6. Gopalgonj/ Khulna Peat Lands</t>
+  </si>
+  <si>
+    <t>7a.Sundarbans</t>
+  </si>
+  <si>
+    <t>7b.Chakaria Sundarban</t>
+  </si>
+  <si>
+    <t>8a.Coastal Plains</t>
+  </si>
+  <si>
+    <t>8b.Offshore Islands</t>
+  </si>
+  <si>
+    <t>8c.Narikel Jinjira Coaral Island</t>
+  </si>
+  <si>
+    <t>8d.Meghna Eastuarine Floodplain</t>
+  </si>
+  <si>
+    <t>8e.Sandy Beach/Sand Dunes</t>
+  </si>
+  <si>
+    <t>9a.Chittagong Hills and The CHTs</t>
+  </si>
+  <si>
+    <t>9b.Sylhet Hills</t>
+  </si>
+  <si>
+    <t>9c.Lalmai Tiperah Hills</t>
+  </si>
+  <si>
+    <t>10 Saline Tidal Floodplain</t>
+  </si>
+  <si>
+    <t>11.Major Rivers</t>
+  </si>
+  <si>
+    <t>12.Coastal Marine Water</t>
   </si>
 </sst>
 </file>
@@ -860,7 +860,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="2000" baseline="0"/>
-            <a:t> field refers to "ZoneName" and Attribute value refers to "lgndIdZone' field in shapefile </a:t>
+            <a:t> field refers to "ZoneName" and Attribute value refers to "LegendID' field in shapefile </a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="2000"/>
         </a:p>
@@ -1173,294 +1173,293 @@
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="C26" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1468,10 +1467,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
